--- a/Docs/Desglo� per IRPF.xlsx
+++ b/Docs/Desglo� per IRPF.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Repositoris\C#\Meus\InversionsV2\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CA455F-E165-47A5-9819-211A0B375024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C06CAE-5C9D-400A-A03B-121292D5C516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{D5391FB0-AD89-473B-AA62-C3B5FCAECA9A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{D5391FB0-AD89-473B-AA62-C3B5FCAECA9A}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{C13071D3-7DC4-40C4-95BF-6C65EC911B05}"/>
   </bookViews>
   <sheets>
     <sheet name="Hisenda" sheetId="1" r:id="rId1"/>
     <sheet name="Arcelor" sheetId="2" r:id="rId2"/>
+    <sheet name="IRPF App" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="36">
   <si>
     <t>PiG ---&gt;</t>
   </si>
@@ -103,6 +105,45 @@
   </si>
   <si>
     <t>Dif</t>
+  </si>
+  <si>
+    <t>Id Venda</t>
+  </si>
+  <si>
+    <t>Id Compra</t>
+  </si>
+  <si>
+    <t>Parts Util</t>
+  </si>
+  <si>
+    <t>Data Compra</t>
+  </si>
+  <si>
+    <t>Desp Util</t>
+  </si>
+  <si>
+    <t>Moviments afectats per la renda del 2021</t>
+  </si>
+  <si>
+    <t>Compra Brut Util</t>
+  </si>
+  <si>
+    <t>Compra Net Util</t>
+  </si>
+  <si>
+    <t>Venda Brut Util</t>
+  </si>
+  <si>
+    <t>Venda Net Util</t>
+  </si>
+  <si>
+    <t>PiG Brut</t>
+  </si>
+  <si>
+    <t>PiG Net</t>
+  </si>
+  <si>
+    <t>Participacions utilitzades</t>
   </si>
 </sst>
 </file>
@@ -148,7 +189,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -158,12 +199,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7F7F7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -203,6 +238,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="21">
     <border>
@@ -446,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -507,15 +554,6 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -548,13 +586,6 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -567,6 +598,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -579,16 +613,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -608,6 +639,49 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="2" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="2" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="2" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="2" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -922,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{386CFA17-404F-4DA8-8891-F2A744C8D48D}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="8.08984375" bestFit="1" customWidth="1"/>
@@ -936,37 +1010,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" thickBot="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="44" t="s">
+      <c r="E1" s="25"/>
+      <c r="F1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="46" t="s">
+      <c r="H1" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="I1" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="47" t="s">
+      <c r="J1" s="39" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="13">
+      <c r="A2" s="64">
         <v>43802</v>
       </c>
       <c r="B2" s="13">
@@ -978,27 +1052,24 @@
       <c r="D2" s="15">
         <v>8805.32</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="26">
         <v>43802</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="31">
+      <c r="H2" s="28">
         <v>500</v>
       </c>
-      <c r="I2" s="32">
+      <c r="I2" s="29">
         <v>7669.06</v>
       </c>
-      <c r="J2" s="33">
+      <c r="J2" s="30">
         <v>900</v>
       </c>
-      <c r="K2">
-        <v>178</v>
-      </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="16">
+      <c r="A3" s="65">
         <v>43802</v>
       </c>
       <c r="B3" s="16">
@@ -1010,24 +1081,28 @@
       <c r="D3" s="18">
         <v>2630.16</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="71">
         <v>43802</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="36">
+      <c r="H3" s="73">
         <v>660</v>
       </c>
-      <c r="I3" s="37">
+      <c r="I3" s="74">
         <v>10117.41</v>
       </c>
-      <c r="J3" s="38">
+      <c r="J3" s="75">
         <v>1560</v>
       </c>
+      <c r="K3" s="82">
+        <f>'IRPF App'!G2+'IRPF App'!G3</f>
+        <v>308</v>
+      </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="19">
+      <c r="A4" s="66">
         <v>43893</v>
       </c>
       <c r="B4" s="19">
@@ -1039,48 +1114,52 @@
       <c r="D4" s="21">
         <v>12378.91</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="71">
         <v>43802</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="36">
+      <c r="H4" s="73">
         <v>92</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="74">
         <v>1414.68</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="75">
         <v>1652</v>
       </c>
+      <c r="K4" s="82">
+        <f>'IRPF App'!G4</f>
+        <v>92</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1">
-      <c r="A5" s="22">
+      <c r="A5" s="67">
         <v>43893</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="68">
         <v>44559</v>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="69">
         <v>891.11</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="70">
         <v>1915.44</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="31">
         <v>43872</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="G5" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="36">
+      <c r="H5" s="33">
         <v>1252</v>
       </c>
-      <c r="I5" s="37">
+      <c r="I5" s="34">
         <v>20781.68</v>
       </c>
-      <c r="J5" s="38">
+      <c r="J5" s="35">
         <v>400</v>
       </c>
     </row>
@@ -1093,20 +1172,24 @@
         <f>SUM(D2:D5)</f>
         <v>25729.829999999998</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="71">
         <v>43893</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="73">
         <v>433</v>
       </c>
-      <c r="I6" s="37">
+      <c r="I6" s="74">
         <v>5760.89</v>
       </c>
-      <c r="J6" s="38">
+      <c r="J6" s="75">
         <v>833</v>
+      </c>
+      <c r="K6" s="82">
+        <f>'IRPF App'!G5</f>
+        <v>433</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1117,55 +1200,77 @@
         <f>D6-C6</f>
         <v>12941.689999999997</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="71">
         <v>43893</v>
       </c>
-      <c r="G7" s="35" t="s">
+      <c r="G7" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="73">
         <v>500</v>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="74">
         <v>6650.06</v>
       </c>
-      <c r="J7" s="38">
+      <c r="J7" s="75">
         <v>1333</v>
       </c>
+      <c r="K7" s="82">
+        <f>'IRPF App'!G6</f>
+        <v>67</v>
+      </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="F8" s="34">
+      <c r="F8" s="31">
         <v>43893</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="33">
         <v>567</v>
       </c>
-      <c r="I8" s="37">
+      <c r="I8" s="34">
         <v>7538.79</v>
       </c>
-      <c r="J8" s="38">
+      <c r="J8" s="35">
         <v>1900</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" thickBot="1">
-      <c r="F9" s="39">
+      <c r="F9" s="76">
         <v>44559</v>
       </c>
-      <c r="G9" s="40" t="s">
+      <c r="G9" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="78">
         <v>900</v>
       </c>
-      <c r="I9" s="42">
+      <c r="I9" s="79">
         <v>25729.83</v>
       </c>
-      <c r="J9" s="43">
+      <c r="J9" s="80">
         <v>1000</v>
       </c>
+      <c r="K9" s="83">
+        <f>-H9</f>
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="F11" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="F12" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="82"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1252,7 +1357,7 @@
       <c r="B3" s="3">
         <v>169</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="42" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="4">
@@ -1278,7 +1383,7 @@
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="9">
-        <f t="shared" ref="L3:L27" si="0">L2-E3</f>
+        <f t="shared" ref="L3:L16" si="0">L2-E3</f>
         <v>952</v>
       </c>
     </row>
@@ -1354,7 +1459,7 @@
       <c r="B6" s="3">
         <v>177</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="43" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="4">
@@ -1417,7 +1522,7 @@
         <f>L6+E7</f>
         <v>900</v>
       </c>
-      <c r="M7" s="52">
+      <c r="M7" s="44">
         <v>0</v>
       </c>
     </row>
@@ -1425,7 +1530,7 @@
       <c r="B8" s="3">
         <v>191</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="40" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="4">
@@ -1454,14 +1559,14 @@
         <f t="shared" ref="L8:L13" si="1">L7+E8</f>
         <v>1560</v>
       </c>
-      <c r="M8" s="53">
+      <c r="M8" s="45">
         <f>E10-L7</f>
         <v>352</v>
       </c>
-      <c r="N8" s="49">
+      <c r="N8" s="41">
         <v>54</v>
       </c>
-      <c r="O8" s="55">
+      <c r="O8" s="47">
         <f>E8-M8-N8</f>
         <v>254</v>
       </c>
@@ -1471,7 +1576,7 @@
       <c r="B9" s="3">
         <v>190</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="40" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="4">
@@ -1500,7 +1605,7 @@
         <f t="shared" si="1"/>
         <v>1652</v>
       </c>
-      <c r="M9" s="55">
+      <c r="M9" s="47">
         <f>E9</f>
         <v>92</v>
       </c>
@@ -1509,7 +1614,7 @@
       <c r="B10" s="3">
         <v>179</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="44" t="s">
         <v>2</v>
       </c>
       <c r="D10" s="4">
@@ -1543,7 +1648,7 @@
       <c r="B11" s="3">
         <v>193</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="40" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="4">
@@ -1572,7 +1677,7 @@
         <f t="shared" si="1"/>
         <v>833</v>
       </c>
-      <c r="M11" s="55">
+      <c r="M11" s="47">
         <f>E11</f>
         <v>433</v>
       </c>
@@ -1581,7 +1686,7 @@
       <c r="B12" s="3">
         <v>192</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="40" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="4">
@@ -1610,7 +1715,7 @@
         <f t="shared" si="1"/>
         <v>1333</v>
       </c>
-      <c r="M12" s="55">
+      <c r="M12" s="47">
         <f>E16-O8-M9-M11</f>
         <v>67</v>
       </c>
@@ -1683,10 +1788,10 @@
         <f>L13</f>
         <v>1900</v>
       </c>
-      <c r="M14" s="56" t="s">
+      <c r="M14" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="N14" s="57" t="s">
+      <c r="N14" s="49" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1694,7 +1799,7 @@
       <c r="B15" s="3">
         <v>206</v>
       </c>
-      <c r="C15" s="49" t="s">
+      <c r="C15" s="41" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="4">
@@ -1723,11 +1828,11 @@
         <f t="shared" si="0"/>
         <v>1846</v>
       </c>
-      <c r="M15" s="58">
+      <c r="M15" s="50">
         <f>N8*F8</f>
         <v>826.74</v>
       </c>
-      <c r="N15" s="59">
+      <c r="N15" s="51">
         <f>G15</f>
         <v>1544.4</v>
       </c>
@@ -1736,7 +1841,7 @@
       <c r="B16" s="3">
         <v>207</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="46" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="4">
@@ -1765,11 +1870,11 @@
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="M16" s="60">
+      <c r="M16" s="52">
         <f>O8*F8+M9*F9+M11*F11+M12*F12</f>
         <v>11942.51</v>
       </c>
-      <c r="N16" s="61">
+      <c r="N16" s="53">
         <f>G16</f>
         <v>24195.599999999999</v>
       </c>
@@ -1786,11 +1891,11 @@
       <c r="J17" s="5"/>
       <c r="K17" s="3"/>
       <c r="L17" s="9"/>
-      <c r="M17" s="62">
+      <c r="M17" s="54">
         <f>SUM(M15:M16)</f>
         <v>12769.25</v>
       </c>
-      <c r="N17" s="63">
+      <c r="N17" s="55">
         <f>SUM(N15:N16)</f>
         <v>25740</v>
       </c>
@@ -1807,10 +1912,10 @@
       <c r="J18" s="5"/>
       <c r="K18" s="3"/>
       <c r="L18" s="9"/>
-      <c r="M18" s="64" t="s">
+      <c r="M18" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="N18" s="65">
+      <c r="N18" s="57">
         <f>N17-M17</f>
         <v>12970.75</v>
       </c>
@@ -1827,10 +1932,10 @@
       <c r="J19" s="5"/>
       <c r="K19" s="3"/>
       <c r="L19" s="9"/>
-      <c r="M19" s="66" t="s">
+      <c r="M19" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="N19" s="59">
+      <c r="N19" s="51">
         <f>J8/E8*(N8+O8)+J9+J11+J12/E12*M12+J15+J16</f>
         <v>29.384039999999999</v>
       </c>
@@ -1851,10 +1956,10 @@
       <c r="J20" s="5"/>
       <c r="K20" s="3"/>
       <c r="L20" s="9"/>
-      <c r="M20" s="66" t="s">
+      <c r="M20" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="N20" s="59">
+      <c r="N20" s="51">
         <f>+N18-N19</f>
         <v>12941.365959999999</v>
       </c>
@@ -1875,10 +1980,10 @@
       <c r="J21" s="5"/>
       <c r="K21" s="3"/>
       <c r="L21" s="9"/>
-      <c r="M21" s="66" t="s">
+      <c r="M21" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="N21" s="59">
+      <c r="N21" s="51">
         <f>Hisenda!D7</f>
         <v>12941.689999999997</v>
       </c>
@@ -1899,10 +2004,10 @@
       <c r="J22" s="5"/>
       <c r="K22" s="3"/>
       <c r="L22" s="9"/>
-      <c r="M22" s="67" t="s">
+      <c r="M22" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="N22" s="68">
+      <c r="N22" s="60">
         <f>+N20-N21</f>
         <v>-0.32403999999769439</v>
       </c>
@@ -2001,4 +2106,428 @@
     <ignoredError sqref="N21" formula="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7F8B7BD-8F98-4036-8A95-8D0CC6039C3D}">
+  <dimension ref="B1:O13"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="2.54296875" customWidth="1"/>
+    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.08984375" customWidth="1"/>
+    <col min="14" max="15" width="10.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" ht="29">
+      <c r="B1" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="63" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="63" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="63" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="63" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15">
+      <c r="B2">
+        <v>206</v>
+      </c>
+      <c r="C2">
+        <v>191</v>
+      </c>
+      <c r="D2" s="61">
+        <v>43802</v>
+      </c>
+      <c r="E2">
+        <v>660</v>
+      </c>
+      <c r="F2" s="62">
+        <v>15.31</v>
+      </c>
+      <c r="G2">
+        <v>54</v>
+      </c>
+      <c r="H2" s="62">
+        <v>0.83</v>
+      </c>
+      <c r="I2" s="62">
+        <v>826.74</v>
+      </c>
+      <c r="J2" s="62">
+        <v>827.57</v>
+      </c>
+      <c r="K2" s="62">
+        <v>1544.4</v>
+      </c>
+      <c r="L2" s="62">
+        <v>1543.79</v>
+      </c>
+      <c r="N2" s="62">
+        <f>K2-I2</f>
+        <v>717.66000000000008</v>
+      </c>
+      <c r="O2" s="62">
+        <f>L2-J2</f>
+        <v>716.21999999999991</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15">
+      <c r="B3">
+        <v>207</v>
+      </c>
+      <c r="C3">
+        <v>191</v>
+      </c>
+      <c r="D3" s="61">
+        <v>43802</v>
+      </c>
+      <c r="E3">
+        <v>660</v>
+      </c>
+      <c r="F3" s="62">
+        <v>15.31</v>
+      </c>
+      <c r="G3">
+        <v>254</v>
+      </c>
+      <c r="H3" s="62">
+        <v>3.91</v>
+      </c>
+      <c r="I3" s="62">
+        <v>3888.74</v>
+      </c>
+      <c r="J3" s="62">
+        <v>3892.65</v>
+      </c>
+      <c r="K3" s="62">
+        <v>7264.4</v>
+      </c>
+      <c r="L3" s="62">
+        <v>7261.53</v>
+      </c>
+      <c r="N3" s="62">
+        <f t="shared" ref="N3:O6" si="0">K3-I3</f>
+        <v>3375.66</v>
+      </c>
+      <c r="O3" s="62">
+        <f t="shared" si="0"/>
+        <v>3368.8799999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15">
+      <c r="B4">
+        <v>207</v>
+      </c>
+      <c r="C4">
+        <v>190</v>
+      </c>
+      <c r="D4" s="61">
+        <v>43802</v>
+      </c>
+      <c r="E4">
+        <v>92</v>
+      </c>
+      <c r="F4" s="62">
+        <v>15.32</v>
+      </c>
+      <c r="G4">
+        <v>92</v>
+      </c>
+      <c r="H4" s="62">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="I4" s="62">
+        <v>1409.44</v>
+      </c>
+      <c r="J4" s="62">
+        <v>1414.5</v>
+      </c>
+      <c r="K4" s="62">
+        <v>2631.2</v>
+      </c>
+      <c r="L4" s="62">
+        <v>2630.16</v>
+      </c>
+      <c r="N4" s="62">
+        <f t="shared" si="0"/>
+        <v>1221.7599999999998</v>
+      </c>
+      <c r="O4" s="62">
+        <f t="shared" si="0"/>
+        <v>1215.6599999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15">
+      <c r="B5">
+        <v>207</v>
+      </c>
+      <c r="C5">
+        <v>193</v>
+      </c>
+      <c r="D5" s="61">
+        <v>43893</v>
+      </c>
+      <c r="E5">
+        <v>433</v>
+      </c>
+      <c r="F5" s="62">
+        <v>13.29</v>
+      </c>
+      <c r="G5">
+        <v>433</v>
+      </c>
+      <c r="H5" s="62">
+        <v>8.06</v>
+      </c>
+      <c r="I5" s="62">
+        <v>5754.57</v>
+      </c>
+      <c r="J5" s="62">
+        <v>5762.63</v>
+      </c>
+      <c r="K5" s="62">
+        <v>12383.8</v>
+      </c>
+      <c r="L5" s="62">
+        <v>12378.91</v>
+      </c>
+      <c r="N5" s="62">
+        <f t="shared" si="0"/>
+        <v>6629.23</v>
+      </c>
+      <c r="O5" s="62">
+        <f t="shared" si="0"/>
+        <v>6616.28</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15">
+      <c r="B6">
+        <v>207</v>
+      </c>
+      <c r="C6">
+        <v>192</v>
+      </c>
+      <c r="D6" s="61">
+        <v>43893</v>
+      </c>
+      <c r="E6">
+        <v>500</v>
+      </c>
+      <c r="F6" s="62">
+        <v>13.28</v>
+      </c>
+      <c r="G6">
+        <v>67</v>
+      </c>
+      <c r="H6" s="62">
+        <v>1.35</v>
+      </c>
+      <c r="I6" s="62">
+        <v>889.76</v>
+      </c>
+      <c r="J6" s="62">
+        <v>891.11</v>
+      </c>
+      <c r="K6" s="62">
+        <v>1916.2</v>
+      </c>
+      <c r="L6" s="62">
+        <v>1915.44</v>
+      </c>
+      <c r="N6" s="62">
+        <f t="shared" si="0"/>
+        <v>1026.44</v>
+      </c>
+      <c r="O6" s="62">
+        <f t="shared" si="0"/>
+        <v>1024.33</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15">
+      <c r="N7" s="62">
+        <f>SUM(N2:N6)</f>
+        <v>12970.75</v>
+      </c>
+      <c r="O7" s="62">
+        <f>SUM(O2:O6)</f>
+        <v>12941.369999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="C8">
+        <f>C3</f>
+        <v>191</v>
+      </c>
+      <c r="D8" s="61">
+        <f>D3</f>
+        <v>43802</v>
+      </c>
+      <c r="F8" s="62">
+        <f>F3</f>
+        <v>15.31</v>
+      </c>
+      <c r="G8">
+        <f>G2+G3</f>
+        <v>308</v>
+      </c>
+      <c r="H8">
+        <f>H2+H3</f>
+        <v>4.74</v>
+      </c>
+      <c r="I8" s="62">
+        <f>G8*F8</f>
+        <v>4715.4800000000005</v>
+      </c>
+      <c r="J8" s="62">
+        <f>I8+H8</f>
+        <v>4720.22</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="C9">
+        <f>C4</f>
+        <v>190</v>
+      </c>
+      <c r="D9" s="61">
+        <f>D4</f>
+        <v>43802</v>
+      </c>
+      <c r="F9" s="62">
+        <f>F4</f>
+        <v>15.32</v>
+      </c>
+      <c r="G9">
+        <f>G4</f>
+        <v>92</v>
+      </c>
+      <c r="H9">
+        <f>H4</f>
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="I9" s="62">
+        <f t="shared" ref="I9:I11" si="1">G9*F9</f>
+        <v>1409.44</v>
+      </c>
+      <c r="J9" s="62">
+        <f t="shared" ref="J9:J11" si="2">I9+H9</f>
+        <v>1414.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15">
+      <c r="C10">
+        <f t="shared" ref="C10:D11" si="3">C5</f>
+        <v>193</v>
+      </c>
+      <c r="D10" s="61">
+        <f t="shared" si="3"/>
+        <v>43893</v>
+      </c>
+      <c r="F10" s="62">
+        <f t="shared" ref="F10" si="4">F5</f>
+        <v>13.29</v>
+      </c>
+      <c r="G10">
+        <f t="shared" ref="G10:H11" si="5">G5</f>
+        <v>433</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="5"/>
+        <v>8.06</v>
+      </c>
+      <c r="I10" s="62">
+        <f t="shared" si="1"/>
+        <v>5754.57</v>
+      </c>
+      <c r="J10" s="62">
+        <f t="shared" si="2"/>
+        <v>5762.63</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15">
+      <c r="C11">
+        <f t="shared" si="3"/>
+        <v>192</v>
+      </c>
+      <c r="D11" s="61">
+        <f t="shared" si="3"/>
+        <v>43893</v>
+      </c>
+      <c r="F11" s="62">
+        <f t="shared" ref="F11" si="6">F6</f>
+        <v>13.28</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="5"/>
+        <v>67</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="5"/>
+        <v>1.35</v>
+      </c>
+      <c r="I11" s="62">
+        <f t="shared" si="1"/>
+        <v>889.76</v>
+      </c>
+      <c r="J11" s="62">
+        <f t="shared" si="2"/>
+        <v>891.11</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15">
+      <c r="J12" s="62">
+        <f>SUM(J8:J11)</f>
+        <v>12788.460000000001</v>
+      </c>
+      <c r="L12" s="62">
+        <f>SUM(L2:L11)</f>
+        <v>25729.829999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15">
+      <c r="L13" s="62"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Docs/Desglo� per IRPF.xlsx
+++ b/Docs/Desglo� per IRPF.xlsx
@@ -8,10 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Repositoris\C#\Meus\InversionsV2\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C06CAE-5C9D-400A-A03B-121292D5C516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AC34FF-3CD9-48C6-A569-53166343FB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{D5391FB0-AD89-473B-AA62-C3B5FCAECA9A}"/>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{C13071D3-7DC4-40C4-95BF-6C65EC911B05}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{D5391FB0-AD89-473B-AA62-C3B5FCAECA9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hisenda" sheetId="1" r:id="rId1"/>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
   <si>
     <t>PiG ---&gt;</t>
   </si>
@@ -144,6 +143,15 @@
   </si>
   <si>
     <t>Participacions utilitzades</t>
+  </si>
+  <si>
+    <t>Desp C</t>
+  </si>
+  <si>
+    <t>Desp V</t>
+  </si>
+  <si>
+    <t>Desp Ut</t>
   </si>
 </sst>
 </file>
@@ -493,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -682,6 +690,8 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -996,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{386CFA17-404F-4DA8-8891-F2A744C8D48D}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="8.08984375" bestFit="1" customWidth="1"/>
@@ -1238,6 +1248,10 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" thickBot="1">
+      <c r="A9" s="62"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
       <c r="F9" s="76">
         <v>44559</v>
       </c>
@@ -1258,7 +1272,17 @@
         <v>-900</v>
       </c>
     </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="62"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+    </row>
     <row r="11" spans="1:11">
+      <c r="A11" s="62"/>
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
       <c r="F11" s="81" t="s">
         <v>28</v>
       </c>
@@ -1267,10 +1291,38 @@
       <c r="I11" s="81"/>
     </row>
     <row r="12" spans="1:11">
+      <c r="A12" s="62"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
       <c r="F12" s="82" t="s">
         <v>35</v>
       </c>
       <c r="G12" s="82"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="62"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="D14" s="62"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="D15" s="62"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="D16" s="62"/>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" s="62"/>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" s="62"/>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" s="62"/>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" s="85"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1280,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D9BEC9-2BA1-4AC7-AE63-E9CBF2F6D6B4}">
-  <dimension ref="B1:P28"/>
+  <dimension ref="B1:S28"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="0" hidden="1" customWidth="1"/>
@@ -1294,11 +1346,10 @@
     <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="1.26953125" customWidth="1"/>
     <col min="13" max="14" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="3.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16">
+    <row r="1" spans="2:19">
       <c r="D1" s="12" t="s">
         <v>4</v>
       </c>
@@ -1319,7 +1370,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:16">
+    <row r="2" spans="2:19">
       <c r="B2" s="3">
         <v>166</v>
       </c>
@@ -1353,7 +1404,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="3" spans="2:16">
+    <row r="3" spans="2:19">
       <c r="B3" s="3">
         <v>169</v>
       </c>
@@ -1387,7 +1438,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="4" spans="2:16">
+    <row r="4" spans="2:19">
       <c r="B4" s="3">
         <v>174</v>
       </c>
@@ -1421,7 +1472,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="5" spans="2:16">
+    <row r="5" spans="2:19">
       <c r="B5" s="6">
         <v>176</v>
       </c>
@@ -1455,7 +1506,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="6" spans="2:16">
+    <row r="6" spans="2:19">
       <c r="B6" s="3">
         <v>177</v>
       </c>
@@ -1489,7 +1540,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="7" spans="2:16">
+    <row r="7" spans="2:19">
       <c r="B7" s="3">
         <v>178</v>
       </c>
@@ -1525,8 +1576,17 @@
       <c r="M7" s="44">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="2:16">
+      <c r="Q7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R7" t="s">
+        <v>37</v>
+      </c>
+      <c r="S7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19">
       <c r="B8" s="3">
         <v>191</v>
       </c>
@@ -1570,9 +1630,24 @@
         <f>E8-M8-N8</f>
         <v>254</v>
       </c>
-      <c r="P8" s="9"/>
-    </row>
-    <row r="9" spans="2:16">
+      <c r="P8" s="9">
+        <f>SUM(N8:O8)</f>
+        <v>308</v>
+      </c>
+      <c r="Q8" s="62">
+        <f>J8/E8*P8</f>
+        <v>4.7459999999999996</v>
+      </c>
+      <c r="R8" s="62">
+        <f>J15+J16/E16*O8</f>
+        <v>3.4802600472813237</v>
+      </c>
+      <c r="S8" s="62">
+        <f>+Q8+R8</f>
+        <v>8.2262600472813237</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19">
       <c r="B9" s="3">
         <v>190</v>
       </c>
@@ -1609,8 +1684,24 @@
         <f>E9</f>
         <v>92</v>
       </c>
-    </row>
-    <row r="10" spans="2:16">
+      <c r="P9" s="9">
+        <f>SUM(M9:O9)</f>
+        <v>92</v>
+      </c>
+      <c r="Q9" s="62">
+        <f>J9</f>
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="R9" s="62">
+        <f>J$16/E$16*M9</f>
+        <v>1.0396217494089834</v>
+      </c>
+      <c r="S9" s="62">
+        <f t="shared" ref="S9:S12" si="2">+Q9+R9</f>
+        <v>6.0996217494089828</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19">
       <c r="B10" s="3">
         <v>179</v>
       </c>
@@ -1643,8 +1734,9 @@
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-    </row>
-    <row r="11" spans="2:16">
+      <c r="S10" s="62"/>
+    </row>
+    <row r="11" spans="2:19">
       <c r="B11" s="3">
         <v>193</v>
       </c>
@@ -1681,8 +1773,24 @@
         <f>E11</f>
         <v>433</v>
       </c>
-    </row>
-    <row r="12" spans="2:16">
+      <c r="P11" s="9">
+        <f>SUM(M11:O11)</f>
+        <v>433</v>
+      </c>
+      <c r="Q11" s="62">
+        <f>J11</f>
+        <v>8.06</v>
+      </c>
+      <c r="R11" s="62">
+        <f>J$16/E$16*M11</f>
+        <v>4.8930023640661942</v>
+      </c>
+      <c r="S11" s="62">
+        <f t="shared" si="2"/>
+        <v>12.953002364066194</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19">
       <c r="B12" s="3">
         <v>192</v>
       </c>
@@ -1719,8 +1827,24 @@
         <f>E16-O8-M9-M11</f>
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1">
+      <c r="P12" s="9">
+        <f>SUM(M12:O12)</f>
+        <v>67</v>
+      </c>
+      <c r="Q12" s="62">
+        <f>J12/E12*P12</f>
+        <v>1.3480400000000001</v>
+      </c>
+      <c r="R12" s="62">
+        <f>J$16/E$16*M12</f>
+        <v>0.75711583924349879</v>
+      </c>
+      <c r="S12" s="62">
+        <f t="shared" si="2"/>
+        <v>2.105155839243499</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" ht="15" thickBot="1">
       <c r="B13" s="3">
         <v>182</v>
       </c>
@@ -1755,7 +1879,7 @@
       </c>
       <c r="M13" s="9"/>
     </row>
-    <row r="14" spans="2:16">
+    <row r="14" spans="2:19">
       <c r="B14" s="6">
         <v>195</v>
       </c>
@@ -1795,7 +1919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:16">
+    <row r="15" spans="2:19">
       <c r="B15" s="3">
         <v>206</v>
       </c>
@@ -1836,8 +1960,12 @@
         <f>G15</f>
         <v>1544.4</v>
       </c>
-    </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1">
+      <c r="Q15" s="62">
+        <f>J15</f>
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" ht="15" thickBot="1">
       <c r="B16" s="3">
         <v>207</v>
       </c>
@@ -1878,8 +2006,12 @@
         <f>G16</f>
         <v>24195.599999999999</v>
       </c>
-    </row>
-    <row r="17" spans="2:14" ht="15" thickBot="1">
+      <c r="Q16" s="62">
+        <f>J16</f>
+        <v>9.56</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" ht="15" thickBot="1">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="4"/>
@@ -1899,8 +2031,12 @@
         <f>SUM(N15:N16)</f>
         <v>25740</v>
       </c>
-    </row>
-    <row r="18" spans="2:14">
+      <c r="Q17" s="84">
+        <f>SUM(Q8:Q16)</f>
+        <v>29.384039999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="4"/>
@@ -1920,7 +2056,7 @@
         <v>12970.75</v>
       </c>
     </row>
-    <row r="19" spans="2:14">
+    <row r="19" spans="2:17">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="4"/>
@@ -1940,7 +2076,7 @@
         <v>29.384039999999999</v>
       </c>
     </row>
-    <row r="20" spans="2:14">
+    <row r="20" spans="2:17">
       <c r="B20" s="3">
         <v>208</v>
       </c>
@@ -1964,7 +2100,7 @@
         <v>12941.365959999999</v>
       </c>
     </row>
-    <row r="21" spans="2:14">
+    <row r="21" spans="2:17">
       <c r="B21" s="3">
         <v>209</v>
       </c>
@@ -1988,7 +2124,7 @@
         <v>12941.689999999997</v>
       </c>
     </row>
-    <row r="22" spans="2:14" ht="15" thickBot="1">
+    <row r="22" spans="2:17" ht="15" thickBot="1">
       <c r="B22" s="3">
         <v>210</v>
       </c>
@@ -2012,7 +2148,7 @@
         <v>-0.32403999999769439</v>
       </c>
     </row>
-    <row r="23" spans="2:14">
+    <row r="23" spans="2:17">
       <c r="B23" s="3">
         <v>211</v>
       </c>
@@ -2029,7 +2165,7 @@
       <c r="K23" s="3"/>
       <c r="L23" s="9"/>
     </row>
-    <row r="24" spans="2:14">
+    <row r="24" spans="2:17">
       <c r="B24" s="3">
         <v>212</v>
       </c>
@@ -2046,7 +2182,7 @@
       <c r="K24" s="3"/>
       <c r="L24" s="9"/>
     </row>
-    <row r="25" spans="2:14">
+    <row r="25" spans="2:17">
       <c r="B25" s="3">
         <v>213</v>
       </c>
@@ -2063,7 +2199,7 @@
       <c r="K25" s="3"/>
       <c r="L25" s="9"/>
     </row>
-    <row r="26" spans="2:14">
+    <row r="26" spans="2:17">
       <c r="B26" s="3">
         <v>214</v>
       </c>
@@ -2080,7 +2216,7 @@
       <c r="K26" s="3"/>
       <c r="L26" s="9"/>
     </row>
-    <row r="27" spans="2:14">
+    <row r="27" spans="2:17">
       <c r="B27" s="3">
         <v>215</v>
       </c>
@@ -2097,11 +2233,12 @@
       <c r="K27" s="3"/>
       <c r="L27" s="9"/>
     </row>
-    <row r="28" spans="2:14">
+    <row r="28" spans="2:17">
       <c r="E28" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="N21" formula="1"/>
   </ignoredErrors>

--- a/Docs/Desglo� per IRPF.xlsx
+++ b/Docs/Desglo� per IRPF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Repositoris\C#\Meus\InversionsV2\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AC34FF-3CD9-48C6-A569-53166343FB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB9BE59-CE3A-405D-8384-0EC5B15C90BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{D5391FB0-AD89-473B-AA62-C3B5FCAECA9A}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5391FB0-AD89-473B-AA62-C3B5FCAECA9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hisenda" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="40">
   <si>
     <t>PiG ---&gt;</t>
   </si>
@@ -152,6 +152,9 @@
   </si>
   <si>
     <t>Desp Ut</t>
+  </si>
+  <si>
+    <t>Perdues anys anterios</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1012,8 @@
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="2" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="2" customWidth="1"/>
     <col min="6" max="6" width="8.08984375" bestFit="1" customWidth="1"/>
@@ -1248,7 +1252,9 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" thickBot="1">
-      <c r="A9" s="62"/>
+      <c r="A9" s="84" t="s">
+        <v>39</v>
+      </c>
       <c r="B9" s="62"/>
       <c r="C9" s="62"/>
       <c r="D9" s="62"/>
@@ -1273,7 +1279,9 @@
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="62"/>
+      <c r="A10" s="84">
+        <v>5845.75</v>
+      </c>
       <c r="B10" s="62"/>
       <c r="C10" s="62"/>
       <c r="D10" s="62"/>
